--- a/TransactionStatusLookup.xlsx
+++ b/TransactionStatusLookup.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SoapData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4499B30A-C8C9-4A5B-84CB-FF7A150E6488}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DFEC515-D25F-4C79-8EF6-3B415AB3668C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="2" xr2:uid="{C4843EFA-4A09-4103-90F0-961CE8A4C71C}"/>
+    <workbookView xWindow="48360" yWindow="7020" windowWidth="21600" windowHeight="11328" xr2:uid="{C4843EFA-4A09-4103-90F0-961CE8A4C71C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -133,9 +133,6 @@
     <t>12</t>
   </si>
   <si>
-    <t>2025</t>
-  </si>
-  <si>
     <t>Some Data 2</t>
   </si>
   <si>
@@ -404,6 +401,9 @@
   </si>
   <si>
     <t>CCD</t>
+  </si>
+  <si>
+    <t>2029</t>
   </si>
 </sst>
 </file>
@@ -496,9 +496,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -536,7 +536,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -642,7 +642,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -784,7 +784,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -793,28 +793,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59A55C32-2C67-49AC-B7AE-8877BD5AA694}">
   <dimension ref="A1:X2"/>
-  <sheetFormatPr defaultColWidth="26.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="26.265625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="27" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.1328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.1328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.265625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.86328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.59765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.86328125" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="5" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="21" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="26.28515625" style="1"/>
+    <col min="13" max="13" width="5.59765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="21" width="11.86328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.86328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="26.265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -882,15 +882,15 @@
         <v>21</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>22</v>
@@ -923,40 +923,40 @@
         <v>31</v>
       </c>
       <c r="L2" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="R2" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="S2" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="T2" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="U2" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="U2" s="1" t="s">
+      <c r="V2" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="V2" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="W2" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -975,20 +975,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69006B40-142A-4476-B1C4-1E426020DE91}">
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultColWidth="28" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="28" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="24.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="41.5703125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.59765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.86328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="41.59765625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.1328125" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="16384" width="28" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -996,169 +996,169 @@
         <v>9</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>51</v>
+      <c r="D2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A3" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>53</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>63</v>
-      </c>
       <c r="G3" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A5" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>61</v>
+      <c r="C5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A6" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>57</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1173,31 +1173,31 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7075182-05B4-4009-9687-1CB44BFF4527}">
   <dimension ref="A1:AA4"/>
-  <sheetFormatPr defaultColWidth="41.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="41.59765625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="26.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.85546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.1328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.86328125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9.265625" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13" style="1" customWidth="1"/>
     <col min="8" max="8" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="23" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="41.5703125" style="1"/>
+    <col min="9" max="9" width="7.1328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.59765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.86328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.86328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.59765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.59765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="23" width="6.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="7.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="5.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.73046875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="41.59765625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1214,16 +1214,16 @@
         <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>75</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>8</v>
@@ -1232,13 +1232,13 @@
         <v>6</v>
       </c>
       <c r="L1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>77</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>78</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>12</v>
@@ -1271,24 +1271,24 @@
         <v>21</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>81</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>25</v>
@@ -1297,13 +1297,13 @@
         <v>26</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>83</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>84</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>29</v>
@@ -1312,152 +1312,152 @@
         <v>27</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>30</v>
       </c>
       <c r="N2" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="R2" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="S2" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="T2" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="U2" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="U2" s="1" t="s">
+      <c r="V2" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="V2" s="1" t="s">
+      <c r="W2" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="W2" s="1" t="s">
+      <c r="X2" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="X2" s="1" t="s">
+      <c r="Y2" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="Y2" s="1" t="s">
+      <c r="Z2" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="Z2" s="1" t="s">
+      <c r="AA2" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="A3" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="AA2" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>106</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>27</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>30</v>
       </c>
       <c r="N3" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="P3" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="Q3" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="Q3" s="1" t="s">
+      <c r="R3" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="R3" s="1" t="s">
+      <c r="S3" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="S3" s="1" t="s">
+      <c r="T3" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="T3" s="1" t="s">
+      <c r="U3" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="U3" s="1" t="s">
+      <c r="V3" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="V3" s="1" t="s">
+      <c r="W3" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="W3" s="1" t="s">
+      <c r="X3" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="X3" s="1" t="s">
-        <v>95</v>
-      </c>
       <c r="Y3" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="Z3" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="Z3" s="1" t="s">
+      <c r="AA3" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="A4" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="AA3" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="G4" s="1" t="s">
-        <v>116</v>
-      </c>
       <c r="J4" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>27</v>
@@ -1466,43 +1466,43 @@
         <v>30</v>
       </c>
       <c r="N4" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="V4" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="W4" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="X4" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="Y4" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="P4" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q4" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="R4" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="S4" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="T4" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="U4" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="V4" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="W4" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="X4" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="Y4" s="1" t="s">
+      <c r="Z4" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="Z4" s="1" t="s">
-        <v>119</v>
-      </c>
       <c r="AA4" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
